--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.42</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="B2">
-        <v>0.04347826086956522</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4859154929577465</v>
+        <v>0.2605633802816901</v>
       </c>
       <c r="D2">
-        <v>0.7604166666666666</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F2">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3870967741935484</v>
+        <v>0.3934426229508197</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2605633802816901</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="D2">
-        <v>0.813953488372093</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
